--- a/resources/id_mgr.xlsx
+++ b/resources/id_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SETTING" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="各模块编号占段表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETTING" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="各模块编号占段表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,9 +494,6 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,7 +570,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>id_min</t>
@@ -591,7 +587,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>id_max</t>
@@ -609,7 +604,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>used_min</t>
@@ -622,7 +616,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>used_max</t>
@@ -635,7 +628,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>status</t>
@@ -1088,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,16 +1115,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>item.ItemBase</t>
+          <t>activity.Activity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10000-29999</t>
+          <t>10000-19999</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1143,16 +1135,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>item.Chest</t>
+          <t>assistant.Assistant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11000-11999</t>
+          <t>1-999</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,32 +1155,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>item.Potion</t>
+          <t>combat.spell</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12000-12999</t>
+          <t>101-99999</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>99899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>越界</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>item.Gem</t>
+          <t>hero.Hero</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13000-13999</t>
+          <t>5000-5999</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1196,23 +1188,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>越界</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>item.Equipment</t>
+          <t>item.Chest</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15000-19999</t>
+          <t>11000-11999</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,16 +1215,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>item.Fabao</t>
+          <t>item.Equipment</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28500-29999</t>
+          <t>15000-19999</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1243,32 +1235,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pet.Pet</t>
+          <t>item.Fabao</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3000-3999</t>
+          <t>28500-29999</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pet.PetSpellBook</t>
+          <t>item.Gem</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21000-21999</t>
+          <t>13000-13999</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1283,36 +1275,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hero.Hero</t>
+          <t>item.ItemBase</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5000-5999</t>
+          <t>10000-29999</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quest.Quest</t>
+          <t>item.Potion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000-259999</t>
+          <t>12000-12999</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1323,56 +1315,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mail.MailTemplate</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>10000-39999</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>正常</t>
+          <t>level 2 配 upgrade_costs[0] = 10070 数量 15、upgrade_costs[1] = 10071 数量 3；</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>residence.Residence</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>30000-30999</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>正常</t>
+          <t>level 3 配 upgrade_costs[0] = 10070 数量 30、upgrade_costs[1] = 10071 数量 10；</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>school.School</t>
+          <t>mail.MailTemplate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1-99</t>
+          <t>10000-39999</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>99</v>
+        <v>30000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1383,16 +1349,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>combat.spell</t>
+          <t>pet.Pet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>101-99999</t>
+          <t>3000-3999</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>99899</v>
+        <v>1000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1403,16 +1369,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>activity.Activity</t>
+          <t>pet.PetSpellBook</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10000-19999</t>
+          <t>21000-21999</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1423,18 +1389,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assistant.Assistant</t>
+          <t>quest.Quest</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1-999</t>
+          <t>250000-259999</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>999</v>
+        <v>10000</v>
       </c>
       <c r="D18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>residence.Residence</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30000-30999</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>school.School</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1-99</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>99</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>正常</t>
         </is>

--- a/resources/id_mgr.xlsx
+++ b/resources/id_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETTING" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="各模块编号占段表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SETTING" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="各模块编号占段表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,6 +494,9 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,6 +573,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>id_min</t>
@@ -587,6 +591,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>id_max</t>
@@ -604,6 +609,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>used_min</t>
@@ -616,6 +622,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>used_max</t>
@@ -628,6 +635,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>status</t>
@@ -1080,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,16 +1123,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>activity.Activity</t>
+          <t>item.ItemBase</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10000-19999</t>
+          <t>10000-29999</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1135,16 +1143,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assistant.Assistant</t>
+          <t>item.Chest</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1-999</t>
+          <t>11000-11999</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1155,32 +1163,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>combat.spell</t>
+          <t>item.Potion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101-99999</t>
+          <t>12000-12999</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>99899</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hero.Hero</t>
+          <t>item.Gem</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5000-5999</t>
+          <t>13000-13999</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1188,23 +1196,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>item.Chest</t>
+          <t>item.Equipment</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11000-11999</t>
+          <t>15000-19999</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,16 +1223,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>item.Equipment</t>
+          <t>item.Fabao</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15000-19999</t>
+          <t>28500-29999</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1235,32 +1243,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>item.Fabao</t>
+          <t>pet.Pet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28500-29999</t>
+          <t>3000-3999</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>越界</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>item.Gem</t>
+          <t>pet.PetSpellBook</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13000-13999</t>
+          <t>21000-21999</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1275,36 +1283,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>item.ItemBase</t>
+          <t>hero.Hero</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10000-29999</t>
+          <t>5000-5999</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>越界</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>item.Potion</t>
+          <t>quest.Quest</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12000-12999</t>
+          <t>250000-259999</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1315,30 +1323,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>level 2 配 upgrade_costs[0] = 10070 数量 15、upgrade_costs[1] = 10071 数量 3；</t>
+          <t>mail.MailTemplate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10000-39999</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>level 3 配 upgrade_costs[0] = 10070 数量 30、upgrade_costs[1] = 10071 数量 10；</t>
+          <t>residence.Residence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30000-30999</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mail.MailTemplate</t>
+          <t>school.School</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10000-39999</t>
+          <t>1-99</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30000</v>
+        <v>99</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1349,16 +1383,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pet.Pet</t>
+          <t>combat.spell</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3000-3999</t>
+          <t>101-99999</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1000</v>
+        <v>99899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1369,16 +1403,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pet.PetSpellBook</t>
+          <t>activity.Activity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21000-21999</t>
+          <t>10000-19999</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1389,58 +1423,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quest.Quest</t>
+          <t>assistant.Assistant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>250000-259999</t>
+          <t>1-999</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10000</v>
+        <v>999</v>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>residence.Residence</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>30000-30999</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>school.School</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1-99</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>99</v>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
